--- a/Result/profitability/4102.xlsx
+++ b/Result/profitability/4102.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.18</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.02999999999999999</v>
+        <v>-0.06624999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>20.92875</v>
+        <v>19.85625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,16 +780,16 @@
         <v>-0.2</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.09624999999999997</v>
+        <v>-0.07374999999999998</v>
       </c>
       <c r="N3" t="n">
-        <v>19.31875</v>
+        <v>20.335</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.24</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.10875</v>
+        <v>-0.10625</v>
       </c>
       <c r="N4" t="n">
-        <v>19.0975</v>
+        <v>19.24125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.14</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.09374999999999997</v>
+        <v>-0.06249999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>20.83375</v>
+        <v>20.5775</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.57</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003750000000000003</v>
+        <v>0.01875000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>23.0975</v>
+        <v>24.055</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.64</v>
       </c>
       <c r="M7" t="n">
-        <v>0.09375</v>
+        <v>0.1075</v>
       </c>
       <c r="N7" t="n">
-        <v>27.385</v>
+        <v>27.89125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.53</v>
       </c>
       <c r="M8" t="n">
-        <v>0.16875</v>
+        <v>0.1625</v>
       </c>
       <c r="N8" t="n">
-        <v>30.83875</v>
+        <v>30.315</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>0.2225</v>
       </c>
       <c r="N9" t="n">
-        <v>32.63875</v>
+        <v>32.63874999999999</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>0.31875</v>
       </c>
       <c r="N10" t="n">
-        <v>35.80249999999999</v>
+        <v>35.8025</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>1.43</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6325</v>
+        <v>0.6325000000000001</v>
       </c>
       <c r="N12" t="n">
         <v>43.735</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>153</v>
+      </c>
+      <c r="D75" t="n">
+        <v>119</v>
+      </c>
+      <c r="E75" t="n">
+        <v>34</v>
+      </c>
+      <c r="F75" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="G75" t="n">
+        <v>4</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.37%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>3</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.002499999999999987</v>
+      </c>
+      <c r="N75" t="n">
+        <v>21.58875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.5555555555555556</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-4.190000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1578154425612053</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.19047619047619</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.050000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.08398197460057355</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
